--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486726_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486726_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1574</v>
+        <v>3.4416</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7483</v>
+        <v>2.2312</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4091</v>
+        <v>1.2104</v>
       </c>
       <c r="G2" t="n">
         <v>-2.1327</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7432</v>
+        <v>1.0274</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4684</v>
+        <v>-0.0487</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2748</v>
+        <v>1.0761</v>
       </c>
       <c r="V2" t="n">
         <v>2.8092</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6041</v>
+        <v>0.9144</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0474</v>
+        <v>0.2628</v>
       </c>
       <c r="F3" t="n">
         <v>0.6515</v>
@@ -688,10 +688,10 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2758</v>
+        <v>0.0345</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4691</v>
+        <v>-0.1588</v>
       </c>
       <c r="U3" t="n">
         <v>0.1933</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.184</v>
+        <v>0.7964</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4087</v>
+        <v>0.005</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5927</v>
+        <v>0.7913</v>
       </c>
       <c r="G4" t="n">
         <v>0.3804</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4744</v>
+        <v>0.1379</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7174</v>
+        <v>-0.3037</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2429</v>
+        <v>0.4416</v>
       </c>
       <c r="V4" t="n">
         <v>1.0503</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>G. COMACHIO COACHMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2554</v>
+        <v>0.3524</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2562</v>
+        <v>0.0275</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1936</v>
+        <v>-1.0869</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1447</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0489</v>
+        <v>-1.0038</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0347</v>
+        <v>0.3968</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6141</v>
+        <v>0.1933</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6488</v>
+        <v>0.2035</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.159</v>
+        <v>-1.4837</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7588</v>
+        <v>-0.2764</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4002</v>
+        <v>-1.2072</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2869</v>
+        <v>0.0551</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>-0.0968</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5077</v>
+        <v>0.1519</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3282</v>
+        <v>0.6394</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2455</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3282</v>
+        <v>0.3939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. COMACHIO COACHMAN</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0007</v>
+        <v>0.0586</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1456</v>
+        <v>-0.0485</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1463</v>
+        <v>0.1072</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0869</v>
+        <v>-1.1936</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1447</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0038</v>
+        <v>-1.0489</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3968</v>
+        <v>-0.0347</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1933</v>
+        <v>0.6141</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2035</v>
+        <v>-0.6488</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4837</v>
+        <v>-1.159</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2764</v>
+        <v>-0.7588</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2072</v>
+        <v>-0.4002</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3256</v>
+        <v>0.3448</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3037</v>
+        <v>-0.0139</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0219</v>
+        <v>0.3587</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6394</v>
+        <v>0.3282</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2455</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3939</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.7847</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3535</v>
+        <v>-0.5604</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.274</v>
+        <v>-0.2243</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0547</v>
@@ -1000,13 +1000,13 @@
         <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3088</v>
+        <v>0.1516</v>
       </c>
       <c r="T7" t="n">
-        <v>0.441</v>
+        <v>0.2341</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1322</v>
+        <v>-0.0825</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0401</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1959</v>
+        <v>-1.3407</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.464</v>
+        <v>-1.3606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2681</v>
+        <v>0.0198</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5693</v>
@@ -1078,13 +1078,13 @@
         <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8</v>
+        <v>0.6551</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3591</v>
+        <v>-0.2557</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1591</v>
+        <v>0.9107</v>
       </c>
       <c r="V8" t="n">
         <v>0.3112</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7621</v>
+        <v>-1.758</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3107</v>
+        <v>-1.2073</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4513</v>
+        <v>-0.5507</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6763</v>
@@ -1156,13 +1156,13 @@
         <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2924</v>
+        <v>0.2965</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0275</v>
+        <v>0.131</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2649</v>
+        <v>0.1655</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5712</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9205</v>
+        <v>-2.0523</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2674</v>
+        <v>-2.3207</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3469</v>
+        <v>0.2684</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.721</v>
+        <v>-0.7933</v>
       </c>
       <c r="H10" t="n">
+        <v>-0.2485</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.5448</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.3857</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.3037</v>
       </c>
-      <c r="I10" t="n">
-        <v>-3.0248</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.8298</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9945000000000001</v>
-      </c>
       <c r="L10" t="n">
-        <v>-1.8243</v>
+        <v>-0.6895</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8912</v>
+        <v>-0.4075</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6907</v>
+        <v>-0.5522</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2005</v>
+        <v>0.1447</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.3515</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="S10" t="n">
         <v>-0.1931</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.1239</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.9308</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.6398</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.4407</v>
+        <v>-0.2898</v>
       </c>
       <c r="U10" t="n">
-        <v>0.199</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3538</v>
+        <v>0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2455</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4827</v>
+        <v>-2.4914</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5275</v>
+        <v>-2.8879</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0449</v>
+        <v>0.3965</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7933</v>
+        <v>-2.721</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2485</v>
+        <v>0.3037</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5448</v>
+        <v>-3.0248</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3857</v>
+        <v>-0.8298</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3037</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6895</v>
+        <v>-1.8243</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4075</v>
+        <v>-1.8912</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5522</v>
+        <v>-0.6907</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1447</v>
+        <v>-1.2005</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3515</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5792</v>
+        <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6234</v>
+        <v>0.0689</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>-0.1798</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1268</v>
+        <v>0.2487</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2856</v>
+        <v>0.3538</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>0.2455</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1374</v>
+        <v>-5.3442</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7682</v>
+        <v>-1.975</v>
       </c>
       <c r="F12" t="n">
         <v>-3.3692</v>
@@ -1390,10 +1390,10 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1102</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3583</v>
+        <v>0.1514</v>
       </c>
       <c r="U12" t="n">
         <v>-0.248</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.1805</v>
+        <v>-8.180299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.508900000000001</v>
+        <v>-7.509</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6714000000000002</v>
+        <v>-0.6715999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-12.0334</v>
@@ -1438,13 +1438,13 @@
         <v>-3.7934</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.239999999999998</v>
+        <v>-8.24</v>
       </c>
       <c r="J13" t="n">
         <v>4.907900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.109899999999999</v>
+        <v>3.1099</v>
       </c>
       <c r="L13" t="n">
         <v>1.7977</v>
@@ -1474,16 +1474,16 @@
         <v>-0.8307</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3128</v>
+        <v>3.3127</v>
       </c>
       <c r="V13" t="n">
-        <v>4.266899999999999</v>
+        <v>4.2669</v>
       </c>
       <c r="W13" t="n">
         <v>4.825399999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5584000000000003</v>
+        <v>-0.5584000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.481</v>
+        <v>7.7747</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1834</v>
+        <v>6.8039</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2977</v>
+        <v>0.9708</v>
       </c>
       <c r="G14" t="n">
         <v>5.7376</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.666</v>
+        <v>-0.3724</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1036</v>
+        <v>-0.4831</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5624</v>
+        <v>0.1107</v>
       </c>
       <c r="V14" t="n">
         <v>0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5061</v>
+        <v>5.0343</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3319</v>
+        <v>2.4353</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1743</v>
+        <v>2.599</v>
       </c>
       <c r="G15" t="n">
         <v>3.4414</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8661</v>
+        <v>-0.3379</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5518</v>
+        <v>-0.4484</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3142</v>
+        <v>0.1105</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9993</v>
+        <v>2.9233</v>
       </c>
       <c r="E16" t="n">
-        <v>2.821</v>
+        <v>2.7175</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1783</v>
+        <v>0.2058</v>
       </c>
       <c r="G16" t="n">
         <v>2.1306</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5517</v>
+        <v>0.4758</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0273</v>
+        <v>-0.0761</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5244</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2277</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3864</v>
+        <v>-0.3275</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6472</v>
+        <v>-0.9944</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2608</v>
+        <v>0.6669</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2582</v>
+        <v>-1.6374</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0968</v>
+        <v>-2.6004</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.355</v>
+        <v>0.963</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4673</v>
+        <v>-0.2354</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3045</v>
+        <v>-1.7026</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>1.4672</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7255</v>
+        <v>-1.402</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2077</v>
+        <v>-0.8978</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5178</v>
+        <v>-0.5042</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1585</v>
+        <v>2.7031</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9876</v>
+        <v>-0.1655</v>
       </c>
       <c r="T17" t="n">
-        <v>0.496</v>
+        <v>-0.759</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4915</v>
+        <v>0.5936</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.243</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7106</v>
+        <v>-0.5636</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6998</v>
+        <v>-4.0652</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4104</v>
+        <v>3.5016</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0108</v>
+        <v>1.1816</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5383</v>
+        <v>1.0144</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4725</v>
+        <v>0.1672</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8175</v>
+        <v>1.3491</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0828</v>
+        <v>1.2224</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7347</v>
+        <v>0.1267</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8283</v>
+        <v>-0.1674</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6211</v>
+        <v>-0.208</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2072</v>
+        <v>0.0406</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
+        <v>-3.8616</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.0892</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.1034</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.6831</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.8696</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.8696</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.5792</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.9487</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.8823</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.2277</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7249</v>
+        <v>-1.3739</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9618</v>
+        <v>-2.4746</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2369</v>
+        <v>1.1007</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1816</v>
+        <v>-0.2582</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0144</v>
+        <v>0.0968</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1672</v>
+        <v>-0.355</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3491</v>
+        <v>0.4673</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2224</v>
+        <v>0.3045</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1267</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1674</v>
+        <v>-0.7255</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.208</v>
+        <v>-0.2077</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0406</v>
+        <v>-0.5178</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8616</v>
+        <v>-2.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0892</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2646</v>
+        <v>0.0001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5797</v>
+        <v>-0.3313</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3151</v>
+        <v>0.3314</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8696</v>
+        <v>0.0426</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.8696</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2486</v>
+        <v>-1.4386</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.615</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3663</v>
+        <v>-2.3111</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6374</v>
+        <v>-1.0108</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6004</v>
+        <v>-0.5383</v>
       </c>
       <c r="I20" t="n">
-        <v>0.963</v>
+        <v>-0.4725</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2354</v>
+        <v>0.8175</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7026</v>
+        <v>0.0828</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4672</v>
+        <v>0.7347</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.402</v>
+        <v>-1.8283</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8978</v>
+        <v>-0.6211</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5042</v>
+        <v>-1.2072</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7031</v>
+        <v>0.5792</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7031</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0866</v>
+        <v>0.2206</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3796</v>
+        <v>0.0549</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2929</v>
+        <v>0.1657</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7355</v>
+        <v>-1.7798</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1406</v>
+        <v>-4.6235</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4051</v>
+        <v>2.8437</v>
       </c>
       <c r="G21" t="n">
         <v>2.4484</v>
@@ -2092,13 +2092,13 @@
         <v>2.7031</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0866</v>
+        <v>-0.131</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1036</v>
+        <v>-0.5865</v>
       </c>
       <c r="U21" t="n">
-        <v>0.017</v>
+        <v>0.4555</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0426</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.180399999999999</v>
+        <v>10.2489</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6714999999999982</v>
+        <v>0.6715000000000018</v>
       </c>
       <c r="F22" t="n">
-        <v>7.508999999999999</v>
+        <v>9.577400000000001</v>
       </c>
       <c r="G22" t="n">
         <v>12.0332</v>
       </c>
       <c r="H22" t="n">
-        <v>3.793299999999999</v>
+        <v>3.7933</v>
       </c>
       <c r="I22" t="n">
-        <v>8.239899999999999</v>
+        <v>8.2399</v>
       </c>
       <c r="J22" t="n">
         <v>16.9412</v>
@@ -2161,7 +2161,7 @@
         <v>-1.7978</v>
       </c>
       <c r="P22" t="n">
-        <v>2.896200000000001</v>
+        <v>2.8962</v>
       </c>
       <c r="Q22" t="n">
         <v>-13.5155</v>
@@ -2170,13 +2170,13 @@
         <v>16.4116</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.4819</v>
+        <v>-0.4137</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.3127</v>
+        <v>-3.3126</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8306</v>
+        <v>2.8991</v>
       </c>
       <c r="V22" t="n">
         <v>-4.2671</v>
